--- a/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -588,7 +588,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>•   One transformer per set on TDK ETD 54/28/19 (core B66395, B66396W coil former, 22 pins).</t>
+          <t>•   One transformer per set on TDK PQ 50/50 (core B65981A, B65982E coil former, 12 pins).</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>10.8 A   /   18.2 A</t>
+          <t>10.4 A   /   18.1 A</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>12+13+14 – 15+16+17+18+19</t>
+          <t>7 – 9</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>28.4 A   /   98.9 A</t>
+          <t>28.5 A   /   99.7 A</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>15+16+17+18+19 – 20+21+22</t>
+          <t>10 – 12</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>28.4 A   /   98.9 A</t>
+          <t>28.5 A   /   99.7 A</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>8 – 10</t>
+          <t>4 – 6</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -741,21 +741,21 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>92 mA dc load (VCC)</t>
+          <t>93 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Centre tap: NS2 finish and NS3 start share pins 15, 16, 17, 18 and 19, one Litz bundle of each on a pin.   At most two bundles on a pin: confirm the pin current rating.   NP1: the 3 bundles of a turn are turned over as a group at each layer.</t>
+          <t>Centre tap is made on the PCB by joining pins 9 and 10 — do NOT join them inside the transformer.   One conductor per pin; a secondary pin carries its whole winding current: confirm the pin current rating, or bring the secondary ends straight out.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Coil former TDK B66396W (ETD 54/28/19), 22 pins, with a 2.0 mm partition added between the two sections.   Pin numbers count along one row from pin 1 and back along the other — confirm on the bobbin drawing before winding.</t>
+          <t>Coil former TDK B65982E (PQ 50/50), 12 pins, with a 3.0 mm partition added between the two sections.   The data sheet numbers pins 1, 6, 7 and 12 and marks pin 1; the pins between are counted from them.</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>65.95 µH    ±10 %</t>
+          <t>70.00 µH    ±10 %</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
           <t>2</t>
@@ -844,17 +844,17 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>23.40 µH    ±10 %</t>
+          <t>25.00 µH    ±10 %</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>SECONDARY ALL SHORT (NS2 + NS3).   NAUX open.   Resonant inductor — a target, not a maximum.</t>
+          <t>EACH HALF: NS2 short alone, then NS3 short alone; the other half and NAUX open.   Both must pass.   Resonant inductor — a target, not a maximum.</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>1+2 – 4+5</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -881,21 +881,21 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Test current 16 A, normal temperature</t>
+          <t>Test current 14 A, normal temperature</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Both measured at 1+2 – 4+5 of ONE transformer.   Item 2 is set by the winding and the partition between the two sections: measure it, and each half alone, on the first samples; a thinner partition lowers it.</t>
+          <t>Both measured at 1 – 3 of ONE transformer.   Item 2 is set by the winding and the partition between the two sections: measure it, and each half alone, on the first samples; a thinner partition lowers it.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Item 2 follows the existing production part 26OP-LM83W clause 4-2, "SECONDARY ALL SHORT" — same vendor, same centre-tapped construction.   The auxiliary is NOT shorted.</t>
+          <t>Item 2, each half: in service only one half conducts at a time, and the two halves lie in different layers.   With NS2 and NS3 both shorted the reading is lower (about 23.1 µH estimated): record it, do not hold it to item 2.   The auxiliary is NOT shorted.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>45  to  120 kHz</t>
+          <t>48  to  118 kHz</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Ae  ≥  212 mm²</t>
+          <t>Ae  ≥  208 mm²</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">

--- a/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -755,7 +755,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Coil former TDK B65982E (PQ 50/50), 12 pins, with a 3.0 mm partition added between the two sections.   The data sheet numbers pins 1, 6, 7 and 12 and marks pin 1; the pins between are counted from them.</t>
+          <t>Coil former TDK B65982E (PQ 50/50), 12 pins, with a 3.0 mm partition added between the two sections.   Pin numbers as the data sheet gives them in its view from below, the pin side: pin 1 at the chamfered corner, 1 to 6 in one row and 7 to 12 in the other, 6 facing 7 and 1 facing 12. The data sheet prints 1, 6, 7 and 12; the pins between are counted. Seen from the component side of the board, left and right are exchanged.</t>
         </is>
       </c>
     </row>

--- a/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
+++ b/PQ50/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1_x1.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>15 Ts</t>
+          <t>15 T</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="32" ht="14" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Core, bobbin, wire and winding arrangement are the supplier’s choice, provided sections 3 and 5 are met.</t>
+          <t>The core, coil former and winding arrangement of the reference design set item 3-2. Another construction is acceptable only when sections 3 and 5 are met and the first samples are approved.</t>
         </is>
       </c>
     </row>
